--- a/artfynd/A 58721-2025 artfynd.xlsx
+++ b/artfynd/A 58721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129987652</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129987651</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58721-2025 artfynd.xlsx
+++ b/artfynd/A 58721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129987652</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129987651</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58721-2025 artfynd.xlsx
+++ b/artfynd/A 58721-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129987652</v>
       </c>
       <c r="B2" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129987651</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
